--- a/artfynd/A 33448-2021 artfynd.xlsx
+++ b/artfynd/A 33448-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115629172</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,12 +784,7 @@
         <v>115628842</v>
       </c>
       <c r="B3" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115628849</v>
+        <v>115628848</v>
       </c>
       <c r="B4" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>324249</v>
+        <v>324248</v>
       </c>
       <c r="R4" t="n">
-        <v>6431003</v>
+        <v>6430987</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115628848</v>
+        <v>115628849</v>
       </c>
       <c r="B5" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>324248</v>
+        <v>324249</v>
       </c>
       <c r="R5" t="n">
-        <v>6430987</v>
+        <v>6431003</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
